--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-29T01:40:01.161Z</t>
+    <t>2026-04-29T05:49:54.640Z</t>
   </si>
   <si>
     <t>UL Solutions</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["hero","cards","cards","cards","cards","cards","cards","cards","cards","cards","cards","columns","columns","columns"]</t>
+    <t>["hero","service-grid","cards","cards","cards","cards","cards","cards","cards","cards","cards","columns","columns","columns"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-29T05:49:54.640Z</t>
+    <t>2026-04-29T06:19:01.828Z</t>
   </si>
   <si>
     <t>UL Solutions</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["hero","service-grid","cards","cards","cards","cards","cards","cards","cards","cards","cards","columns","columns","columns"]</t>
+    <t>["hero","service-grid","cards","cards","cards","cards","cards","cards","cards","cards","cards","video-text","columns","columns"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-29T06:19:01.828Z</t>
+    <t>2026-04-29T06:34:10.295Z</t>
   </si>
   <si>
     <t>UL Solutions</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["hero","service-grid","cards","cards","cards","cards","cards","cards","cards","cards","cards","video-text","columns","columns"]</t>
+    <t>["hero","service-grid","spotlight-cards","cards","cards","cards","cards","cards","cards","cards","cards","video-text","columns","columns"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-29T06:34:10.295Z</t>
+    <t>2026-04-29T06:45:43.072Z</t>
   </si>
   <si>
     <t>UL Solutions</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["hero","service-grid","spotlight-cards","cards","cards","cards","cards","cards","cards","cards","cards","video-text","columns","columns"]</t>
+    <t>["hero","service-grid","spotlight-cards","feature-cards","cards","cards","cards","cards","cards","cards","cards","video-text","columns","columns"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-29T06:45:43.072Z</t>
+    <t>2026-04-29T06:53:05.900Z</t>
   </si>
   <si>
     <t>UL Solutions</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-29T06:53:05.900Z</t>
+    <t>2026-04-29T07:13:30.699Z</t>
   </si>
   <si>
     <t>UL Solutions</t>
